--- a/Delhi-March-2026.xlsx
+++ b/Delhi-March-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="86">
   <si>
     <t>Sr. No</t>
   </si>
@@ -118,10 +118,10 @@
     <t>HR38AE5738</t>
   </si>
   <si>
-    <t>HR55AR-0857</t>
-  </si>
-  <si>
-    <t>HR55AR-1793</t>
+    <t>HR55AR0857</t>
+  </si>
+  <si>
+    <t>HR55AR1793</t>
   </si>
   <si>
     <t>MH02FG4092</t>
@@ -142,13 +142,13 @@
     <t>HR55AU6270</t>
   </si>
   <si>
-    <t>MH02FG 4112</t>
-  </si>
-  <si>
-    <t>MH02FG 7817</t>
-  </si>
-  <si>
-    <t>MH02FG 0905</t>
+    <t>MH02FG4112</t>
+  </si>
+  <si>
+    <t>MH02FG7817</t>
+  </si>
+  <si>
+    <t>MH02FG0905</t>
   </si>
   <si>
     <t>MH02GH0253</t>
@@ -172,7 +172,7 @@
     <t>HR55AX5016</t>
   </si>
   <si>
-    <t>DL1N-6505</t>
+    <t>DL1N6505</t>
   </si>
   <si>
     <t>HR38AE9224</t>
@@ -205,7 +205,7 @@
     <t>BYD E6</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>HYCROSS</t>
@@ -235,28 +235,43 @@
     <t>21/04/2023</t>
   </si>
   <si>
+    <t>28/11/2023</t>
+  </si>
+  <si>
+    <t>25/03/2021</t>
+  </si>
+  <si>
+    <t>21/09/2021</t>
+  </si>
+  <si>
+    <t>21/10/2021</t>
+  </si>
+  <si>
+    <t>28/06/2022</t>
+  </si>
+  <si>
+    <t>16/09/2024</t>
+  </si>
+  <si>
+    <t>30/05/2023</t>
+  </si>
+  <si>
+    <t>24/06/2025</t>
+  </si>
+  <si>
+    <t>21/04/2014</t>
+  </si>
+  <si>
+    <t>14/03/2023</t>
+  </si>
+  <si>
+    <t>23/01/2025</t>
+  </si>
+  <si>
+    <t>30/07/2024</t>
+  </si>
+  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>25/03/2021</t>
-  </si>
-  <si>
-    <t>21/09/2021</t>
-  </si>
-  <si>
-    <t>21/10/2021</t>
-  </si>
-  <si>
-    <t>30/05/2023</t>
-  </si>
-  <si>
-    <t>14/03/2023</t>
-  </si>
-  <si>
-    <t>23/01/2025</t>
-  </si>
-  <si>
-    <t>30/07/2024</t>
   </si>
 </sst>
 </file>
@@ -778,7 +793,7 @@
         <v>-77860</v>
       </c>
       <c r="Z2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -1840,8 +1855,8 @@
       <c r="F16" t="s">
         <v>63</v>
       </c>
-      <c r="G16" t="s">
-        <v>73</v>
+      <c r="G16" s="2">
+        <v>44471</v>
       </c>
       <c r="H16">
         <v>91142</v>
@@ -1921,7 +1936,7 @@
         <v>63</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H17">
         <v>65418</v>
@@ -2001,7 +2016,7 @@
         <v>63</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H18">
         <v>18736</v>
@@ -2241,7 +2256,7 @@
         <v>63</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H21">
         <v>22841</v>
@@ -2481,7 +2496,7 @@
         <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H24">
         <v>33364</v>
@@ -2561,7 +2576,7 @@
         <v>64</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H25">
         <v>24922</v>
@@ -2641,7 +2656,7 @@
         <v>65</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2698,7 +2713,7 @@
         <v>0</v>
       </c>
       <c r="Z26" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:26">
@@ -2721,7 +2736,7 @@
         <v>66</v>
       </c>
       <c r="G27" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H27">
         <v>114488</v>
@@ -3121,7 +3136,7 @@
         <v>68</v>
       </c>
       <c r="G32" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H32">
         <v>26205</v>
@@ -3201,7 +3216,7 @@
         <v>69</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H33">
         <v>99833</v>
@@ -3281,7 +3296,7 @@
         <v>69</v>
       </c>
       <c r="G34" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H34">
         <v>86213</v>
@@ -3361,7 +3376,7 @@
         <v>69</v>
       </c>
       <c r="G35" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H35">
         <v>82037</v>
